--- a/test/demo-mar-2025/heatingOrCoolingAndPower/fixtures/consumptions.xlsx
+++ b/test/demo-mar-2025/heatingOrCoolingAndPower/fixtures/consumptions.xlsx
@@ -38,7 +38,7 @@
     <t>Emission Factor</t>
   </si>
   <si>
-    <t>Newcastle</t>
+    <t>Southcastle</t>
   </si>
   <si>
     <t>Jan</t>
@@ -123,7 +123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -134,6 +134,11 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -155,15 +160,18 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -411,7 +419,7 @@
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
@@ -431,7 +439,7 @@
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1">
@@ -451,7 +459,7 @@
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
@@ -471,7 +479,7 @@
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1">
@@ -491,7 +499,7 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1">
@@ -511,7 +519,7 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
@@ -531,7 +539,7 @@
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -551,7 +559,7 @@
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="1">
@@ -571,7 +579,7 @@
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="1">
@@ -591,7 +599,7 @@
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="1">
@@ -611,7 +619,7 @@
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="1">
@@ -631,7 +639,7 @@
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="1">
@@ -651,7 +659,7 @@
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="1">
@@ -671,7 +679,7 @@
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="1">
@@ -691,7 +699,7 @@
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="1">
@@ -711,7 +719,7 @@
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B17" s="1">
@@ -731,7 +739,7 @@
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B18" s="1">
@@ -751,7 +759,7 @@
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="1">
@@ -771,7 +779,7 @@
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B20" s="1">
@@ -791,7 +799,7 @@
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B21" s="1">
@@ -811,7 +819,7 @@
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B22" s="1">
@@ -831,7 +839,7 @@
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B23" s="1">
@@ -851,7 +859,7 @@
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B24" s="1">
@@ -871,7 +879,7 @@
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B25" s="1">
@@ -2261,7 +2269,7 @@
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
@@ -2276,7 +2284,7 @@
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>125.0</v>
       </c>
       <c r="G2" s="1">
@@ -2288,7 +2296,7 @@
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1">
@@ -2303,7 +2311,7 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>145.0</v>
       </c>
       <c r="G3" s="1">
@@ -2315,7 +2323,7 @@
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
@@ -2330,7 +2338,7 @@
       <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>175.0</v>
       </c>
       <c r="G4" s="1">
@@ -2342,7 +2350,7 @@
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1">
@@ -2357,7 +2365,7 @@
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>185.0</v>
       </c>
       <c r="G5" s="1">
@@ -2369,7 +2377,7 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1">
@@ -2384,7 +2392,7 @@
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>205.0</v>
       </c>
       <c r="G6" s="1">
@@ -2396,7 +2404,7 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
@@ -2411,7 +2419,7 @@
       <c r="E7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>225.0</v>
       </c>
       <c r="G7" s="1">
@@ -2423,7 +2431,7 @@
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -2438,7 +2446,7 @@
       <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>190.0</v>
       </c>
       <c r="G8" s="1">
@@ -2450,7 +2458,7 @@
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="1">
@@ -2465,7 +2473,7 @@
       <c r="E9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>170.0</v>
       </c>
       <c r="G9" s="1">
@@ -2477,7 +2485,7 @@
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="1">
@@ -2492,7 +2500,7 @@
       <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>230.0</v>
       </c>
       <c r="G10" s="1">
@@ -2504,7 +2512,7 @@
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="1">
@@ -2519,7 +2527,7 @@
       <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>210.0</v>
       </c>
       <c r="G11" s="1">
@@ -2531,7 +2539,7 @@
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="1">
@@ -2546,7 +2554,7 @@
       <c r="E12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>190.0</v>
       </c>
       <c r="G12" s="1">
@@ -2558,7 +2566,7 @@
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="1">
@@ -2573,7 +2581,7 @@
       <c r="E13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>155.0</v>
       </c>
       <c r="G13" s="1">
@@ -2585,7 +2593,7 @@
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="1">
@@ -2600,7 +2608,7 @@
       <c r="E14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>115.0</v>
       </c>
       <c r="G14" s="1">
@@ -2612,7 +2620,7 @@
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="1">
@@ -2627,7 +2635,7 @@
       <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>145.0</v>
       </c>
       <c r="G15" s="1">
@@ -2639,7 +2647,7 @@
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="1">
@@ -2654,7 +2662,7 @@
       <c r="E16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>195.0</v>
       </c>
       <c r="G16" s="1">
@@ -2666,7 +2674,7 @@
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B17" s="1">
@@ -2681,7 +2689,7 @@
       <c r="E17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>195.0</v>
       </c>
       <c r="G17" s="1">
@@ -2693,7 +2701,7 @@
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B18" s="1">
@@ -2708,7 +2716,7 @@
       <c r="E18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>225.0</v>
       </c>
       <c r="G18" s="1">
@@ -2720,7 +2728,7 @@
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="1">
@@ -2735,7 +2743,7 @@
       <c r="E19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>200.0</v>
       </c>
       <c r="G19" s="1">
@@ -2747,7 +2755,7 @@
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B20" s="1">
@@ -2762,7 +2770,7 @@
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <v>175.0</v>
       </c>
       <c r="G20" s="1">
@@ -2774,7 +2782,7 @@
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B21" s="1">
@@ -2789,7 +2797,7 @@
       <c r="E21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>180.0</v>
       </c>
       <c r="G21" s="1">
@@ -2801,7 +2809,7 @@
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B22" s="1">
@@ -2816,7 +2824,7 @@
       <c r="E22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>170.0</v>
       </c>
       <c r="G22" s="1">
@@ -2828,7 +2836,7 @@
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B23" s="1">
@@ -2843,7 +2851,7 @@
       <c r="E23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <v>290.0</v>
       </c>
       <c r="G23" s="1">
@@ -2855,7 +2863,7 @@
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B24" s="1">
@@ -2870,7 +2878,7 @@
       <c r="E24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
         <v>150.0</v>
       </c>
       <c r="G24" s="1">
@@ -2882,7 +2890,7 @@
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B25" s="1">
@@ -2897,7 +2905,7 @@
       <c r="E25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>145.0</v>
       </c>
       <c r="G25" s="1">
@@ -3897,7 +3905,7 @@
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1">
@@ -3906,13 +3914,13 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>120.0</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -3936,7 +3944,7 @@
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1">
@@ -3945,13 +3953,13 @@
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>150.0</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -3975,7 +3983,7 @@
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="1">
@@ -3984,13 +3992,13 @@
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>180.0</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -4014,7 +4022,7 @@
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1">
@@ -4023,13 +4031,13 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>190.0</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -4053,7 +4061,7 @@
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1">
@@ -4062,13 +4070,13 @@
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>200.0</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -4092,7 +4100,7 @@
       </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1">
@@ -4101,13 +4109,13 @@
       <c r="C7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>210.0</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -4131,7 +4139,7 @@
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="1">
@@ -4140,13 +4148,13 @@
       <c r="C8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>180.0</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -4170,7 +4178,7 @@
       </c>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B9" s="1">
@@ -4179,13 +4187,13 @@
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>190.0</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -4209,7 +4217,7 @@
       </c>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="1">
@@ -4218,13 +4226,13 @@
       <c r="C10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>200.0</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -4248,7 +4256,7 @@
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="1">
@@ -4257,13 +4265,13 @@
       <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>200.0</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -4287,7 +4295,7 @@
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="1">
@@ -4296,13 +4304,13 @@
       <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>220.0</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -4326,7 +4334,7 @@
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B13" s="1">
@@ -4335,13 +4343,13 @@
       <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>175.0</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -4365,7 +4373,7 @@
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B14" s="1">
@@ -4374,13 +4382,13 @@
       <c r="C14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>125.0</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -4404,7 +4412,7 @@
       </c>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="1">
@@ -4413,13 +4421,13 @@
       <c r="C15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>155.0</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -4443,7 +4451,7 @@
       </c>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B16" s="1">
@@ -4452,13 +4460,13 @@
       <c r="C16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>185.0</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -4482,7 +4490,7 @@
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B17" s="1">
@@ -4491,13 +4499,13 @@
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>195.0</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -4521,7 +4529,7 @@
       </c>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B18" s="1">
@@ -4530,13 +4538,13 @@
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>205.0</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -4560,7 +4568,7 @@
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B19" s="1">
@@ -4569,13 +4577,13 @@
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>215.0</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -4599,7 +4607,7 @@
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B20" s="1">
@@ -4608,13 +4616,13 @@
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="4">
         <v>185.0</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -4638,7 +4646,7 @@
       </c>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B21" s="1">
@@ -4647,13 +4655,13 @@
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>195.0</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -4677,7 +4685,7 @@
       </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B22" s="1">
@@ -4686,13 +4694,13 @@
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>205.0</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -4716,7 +4724,7 @@
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B23" s="1">
@@ -4725,13 +4733,13 @@
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <v>225.0</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -4755,7 +4763,7 @@
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B24" s="1">
@@ -4764,13 +4772,13 @@
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
         <v>180.0</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -4794,7 +4802,7 @@
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B25" s="1">
@@ -4803,13 +4811,13 @@
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>155.0</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -4833,7 +4841,7 @@
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B26" s="1">
@@ -4842,13 +4850,13 @@
       <c r="C26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
         <v>120.0</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -4872,7 +4880,7 @@
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B27" s="1">
@@ -4881,13 +4889,13 @@
       <c r="C27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
         <v>150.0</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -4911,7 +4919,7 @@
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B28" s="1">
@@ -4920,13 +4928,13 @@
       <c r="C28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="3">
         <v>180.0</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -4950,7 +4958,7 @@
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B29" s="1">
@@ -4959,13 +4967,13 @@
       <c r="C29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
         <v>190.0</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -4989,7 +4997,7 @@
       </c>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B30" s="1">
@@ -4998,13 +5006,13 @@
       <c r="C30" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>200.0</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -5028,7 +5036,7 @@
       </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B31" s="1">
@@ -5037,13 +5045,13 @@
       <c r="C31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>210.0</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -5067,7 +5075,7 @@
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B32" s="1">
@@ -5076,13 +5084,13 @@
       <c r="C32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="4">
         <v>180.0</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -5106,7 +5114,7 @@
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B33" s="1">
@@ -5115,13 +5123,13 @@
       <c r="C33" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="3">
         <v>190.0</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -5145,7 +5153,7 @@
       </c>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B34" s="1">
@@ -5154,13 +5162,13 @@
       <c r="C34" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="3">
         <v>200.0</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -5184,7 +5192,7 @@
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B35" s="1">
@@ -5193,13 +5201,13 @@
       <c r="C35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="3">
         <v>200.0</v>
       </c>
       <c r="G35" s="1" t="s">
@@ -5223,7 +5231,7 @@
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B36" s="1">
@@ -5232,13 +5240,13 @@
       <c r="C36" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>220.0</v>
       </c>
       <c r="G36" s="1" t="s">
@@ -5262,7 +5270,7 @@
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B37" s="1">
@@ -5271,13 +5279,13 @@
       <c r="C37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="3">
         <v>175.0</v>
       </c>
       <c r="G37" s="1" t="s">
@@ -5301,7 +5309,7 @@
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B38" s="1">
@@ -5310,13 +5318,13 @@
       <c r="C38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="3">
         <v>125.0</v>
       </c>
       <c r="G38" s="1" t="s">
@@ -5340,7 +5348,7 @@
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B39" s="1">
@@ -5349,13 +5357,13 @@
       <c r="C39" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="3">
         <v>155.0</v>
       </c>
       <c r="G39" s="1" t="s">
@@ -5379,7 +5387,7 @@
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B40" s="1">
@@ -5388,13 +5396,13 @@
       <c r="C40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="3">
         <v>185.0</v>
       </c>
       <c r="G40" s="1" t="s">
@@ -5418,7 +5426,7 @@
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B41" s="1">
@@ -5427,13 +5435,13 @@
       <c r="C41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="3">
         <v>195.0</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -5457,7 +5465,7 @@
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B42" s="1">
@@ -5466,13 +5474,13 @@
       <c r="C42" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="3">
         <v>205.0</v>
       </c>
       <c r="G42" s="1" t="s">
@@ -5496,7 +5504,7 @@
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B43" s="1">
@@ -5505,13 +5513,13 @@
       <c r="C43" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="3">
         <v>215.0</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -5535,7 +5543,7 @@
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B44" s="1">
@@ -5544,13 +5552,13 @@
       <c r="C44" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="4">
         <v>185.0</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -5574,7 +5582,7 @@
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B45" s="1">
@@ -5583,13 +5591,13 @@
       <c r="C45" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="3">
         <v>195.0</v>
       </c>
       <c r="G45" s="1" t="s">
@@ -5613,7 +5621,7 @@
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B46" s="1">
@@ -5622,13 +5630,13 @@
       <c r="C46" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="3">
         <v>205.0</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -5652,7 +5660,7 @@
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B47" s="1">
@@ -5661,13 +5669,13 @@
       <c r="C47" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="3">
         <v>225.0</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -5691,7 +5699,7 @@
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B48" s="1">
@@ -5700,13 +5708,13 @@
       <c r="C48" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="3">
         <v>180.0</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -5730,7 +5738,7 @@
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B49" s="1">
@@ -5739,13 +5747,13 @@
       <c r="C49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="3">
         <v>155.0</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -5772,9 +5780,9 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="3"/>
+      <c r="D50" s="4"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="2"/>
+      <c r="F50" s="3"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
